--- a/SCHNIE/SCHNIE管理条目.xlsx
+++ b/SCHNIE/SCHNIE管理条目.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a04d8a5aeffc5f4/第九边缘SCHNIE/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\网站控制\git_pic\pic_bed\SCHNIE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="370" documentId="13_ncr:1_{34915CAB-817A-40B3-9C3A-BE22852CCF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CC0E781-37BF-4455-8DAF-09B8F32D9416}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D27FAA-CE01-48B8-9FD0-483561AB5910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="730" yWindow="3010" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="730" yWindow="3010" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>

--- a/SCHNIE/SCHNIE管理条目.xlsx
+++ b/SCHNIE/SCHNIE管理条目.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\网站控制\git_pic\pic_bed\SCHNIE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a04d8a5aeffc5f4/第九边缘^7生涅/03后继^7九虹文明/外世拓展/星球^7阳汇彼日/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10D27FAA-CE01-48B8-9FD0-483561AB5910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="430" documentId="13_ncr:1_{34915CAB-817A-40B3-9C3A-BE22852CCF45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B35F4D87-6760-4B62-A748-AC433A65E7BC}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="730" yWindow="3010" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="234">
   <si>
     <t>最后操作时间</t>
   </si>
@@ -130,21 +130,6 @@
     <t>四位构造-创造</t>
   </si>
   <si>
-    <t>辩驳对象</t>
-  </si>
-  <si>
-    <t>随意和理性</t>
-  </si>
-  <si>
-    <t>本我与联想</t>
-  </si>
-  <si>
-    <t>他我</t>
-  </si>
-  <si>
-    <t>SCHNIE关于人生的一个判断</t>
-  </si>
-  <si>
     <t>不可预见之核-人生</t>
   </si>
   <si>
@@ -334,10 +319,6 @@
   </si>
   <si>
     <t>混沌空语，闭环未来</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -389,18 +370,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>FOUNDATION_1</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>FOUNDATION_2</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>FOUNDATION_3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>R灵耀体系：金泽范式</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -656,10 +625,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>演奏，优雅而洁净的“谎言”。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>赋予现实含义</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -668,10 +633,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>R灵耀体系：光与流辰</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>光芒会陪着流星，共耀丰富的含义。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -771,18 +732,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>阅读手册、协作测试</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>互选新生信息</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>同“我”的一部分——契约之神签订的崇高而又随性的契约。</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>本恶</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -795,12 +748,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Thoughts_collide_1</t>
-  </si>
-  <si>
-    <t>Thoughts_collide_2</t>
-  </si>
-  <si>
     <t>BACKGROUND_7</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -825,30 +772,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>Thoughts_collide_3</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thoughts_collide_4</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thoughts_collide_5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thoughts_collide_6</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thoughts_collide_7</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thoughts_collide_8</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>离开原有的轨迹；即便是彻底失去后的重新选择，叛离命途的结局只能走向浮影。</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -857,10 +780,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>浮念</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>SCHNIE/生涅</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -906,6 +825,97 @@
   </si>
   <si>
     <t>宏观宇宙观</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>本源、感受与联想</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>辩驳</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>表达</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>SCHNIE2026</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>THEORY_3</t>
+  </si>
+  <si>
+    <t>THEORY_2</t>
+  </si>
+  <si>
+    <t>THEORY_1</t>
+  </si>
+  <si>
+    <t>THOUGHTS_COLLIDE_8</t>
+  </si>
+  <si>
+    <t>THOUGHTS_COLLIDE_7</t>
+  </si>
+  <si>
+    <t>THOUGHTS_COLLIDE_6</t>
+  </si>
+  <si>
+    <t>THOUGHTS_COLLIDE_4</t>
+  </si>
+  <si>
+    <t>THOUGHTS_COLLIDE_3</t>
+  </si>
+  <si>
+    <t>THOUGHTS_COLLIDE_2</t>
+  </si>
+  <si>
+    <t>R第九边缘：光与流辰</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>引导、测试</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>第九边缘：人生行迹</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>D.微型辩驳集</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>四位构造-感知</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>THOUGHTS_COLLIDE_5</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>THOUGHTS_COLLIDE_1</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>不可演算之枝-创造</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>大地在演奏，优雅而洁净的“谎言”。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>同契约之神，签订的崇高而又随性的契约。</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>形路</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -913,7 +923,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -957,6 +967,14 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1085,7 +1103,6 @@
     <xf numFmtId="14" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1122,7 +1139,10 @@
     <xf numFmtId="14" fontId="2" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1400,8 +1420,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AR33"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14"/>
+  <dimension ref="A1:AR31"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" style="2" customWidth="1"/>
     <col min="2" max="2" width="37.08984375" style="2" customWidth="1"/>
@@ -1415,7 +1435,7 @@
     <col min="24" max="24" width="28.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" ht="15">
+    <row r="1" spans="1:44" ht="15" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1437,8 +1457,8 @@
       <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="18" t="s">
-        <v>95</v>
+      <c r="H1" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="I1" s="12"/>
       <c r="J1" s="12" t="s">
@@ -1477,62 +1497,62 @@
       <c r="U1" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="V1" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="W1" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="X1" s="19" t="s">
-        <v>139</v>
+      <c r="V1" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="W1" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="X1" s="18" t="s">
+        <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:44" s="1" customFormat="1">
-      <c r="A2" s="23">
-        <v>45889</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>42</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="23" t="s">
+    <row r="2" spans="1:44" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21">
+        <v>46259</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="23"/>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="W2" s="26" t="s">
-        <v>179</v>
-      </c>
-      <c r="X2" s="26" t="s">
-        <v>181</v>
+      <c r="H2" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="W2" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="X2" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="Y2"/>
       <c r="Z2"/>
@@ -1555,52 +1575,52 @@
       <c r="AQ2"/>
       <c r="AR2"/>
     </row>
-    <row r="3" spans="1:44" s="1" customFormat="1">
-      <c r="A3" s="23">
-        <v>45900</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>86</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="G3" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" s="26" t="s">
-        <v>190</v>
-      </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-      <c r="L3" s="23"/>
-      <c r="M3" s="23"/>
-      <c r="N3" s="23"/>
-      <c r="O3" s="23"/>
-      <c r="P3" s="23"/>
-      <c r="Q3" s="23"/>
-      <c r="R3" s="23"/>
-      <c r="S3" s="23"/>
-      <c r="T3" s="23"/>
-      <c r="U3" s="23"/>
-      <c r="V3" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="W3" s="26" t="s">
-        <v>154</v>
-      </c>
-      <c r="X3" s="26" t="s">
-        <v>188</v>
+    <row r="3" spans="1:44" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21">
+        <v>46259</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="W3" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="X3" s="15" t="s">
+        <v>150</v>
       </c>
       <c r="Y3"/>
       <c r="Z3"/>
@@ -1623,30 +1643,30 @@
       <c r="AQ3"/>
       <c r="AR3"/>
     </row>
-    <row r="4" spans="1:44">
-      <c r="A4" s="27">
-        <v>45900</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>109</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="24" t="s">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A4" s="10">
+        <v>46214</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="H4" s="24" t="s">
-        <v>125</v>
+      <c r="F4" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>215</v>
       </c>
       <c r="I4" s="28"/>
       <c r="J4" s="28"/>
@@ -1661,498 +1681,498 @@
       <c r="S4" s="28"/>
       <c r="T4" s="28"/>
       <c r="U4" s="28"/>
-      <c r="V4" s="24" t="s">
+      <c r="V4" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="W4" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="X4" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A5" s="22">
+        <v>46212</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="F5" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
+      <c r="N5" s="22"/>
+      <c r="O5" s="22"/>
+      <c r="P5" s="22"/>
+      <c r="Q5" s="22"/>
+      <c r="R5" s="22"/>
+      <c r="S5" s="22"/>
+      <c r="T5" s="22"/>
+      <c r="U5" s="22"/>
+      <c r="V5" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="W5" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="X5" s="25" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
+        <v>46059</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="G6" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="14"/>
+      <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
+      <c r="O6" s="14"/>
+      <c r="P6" s="14"/>
+      <c r="Q6" s="14"/>
+      <c r="R6" s="14"/>
+      <c r="S6" s="14"/>
+      <c r="T6" s="14"/>
+      <c r="U6" s="14"/>
+      <c r="V6" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="W6" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="X6" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A7" s="21">
+        <v>46059</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W7" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="X7" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
+        <v>46011</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="W4" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="X4" s="25" t="s">
-        <v>147</v>
+      <c r="E8" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="W8" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="X8" s="13" t="s">
+        <v>174</v>
       </c>
     </row>
-    <row r="5" spans="1:44">
-      <c r="A5" s="23">
-        <v>45905</v>
-      </c>
-      <c r="B5" s="26" t="s">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
+        <v>45997</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
+      <c r="N9" s="11"/>
+      <c r="O9" s="11"/>
+      <c r="P9" s="11"/>
+      <c r="Q9" s="11"/>
+      <c r="R9" s="11"/>
+      <c r="S9" s="11"/>
+      <c r="T9" s="11"/>
+      <c r="U9" s="11"/>
+      <c r="V9" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="W9" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="X9" s="13" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
+        <v>45982</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="11"/>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
+      <c r="N10" s="11"/>
+      <c r="O10" s="11"/>
+      <c r="P10" s="11"/>
+      <c r="Q10" s="11"/>
+      <c r="R10" s="11"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="11"/>
+      <c r="U10" s="11"/>
+      <c r="V10" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="W10" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="X10" s="13" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
+        <v>45941</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="11"/>
+      <c r="O11" s="11"/>
+      <c r="P11" s="11"/>
+      <c r="Q11" s="11"/>
+      <c r="R11" s="11"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="11"/>
+      <c r="U11" s="11"/>
+      <c r="V11" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="W11" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G5" s="23" t="s">
+      <c r="X11" s="13" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
+        <v>45926</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="G12" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="H5" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="23"/>
-      <c r="K5" s="23"/>
-      <c r="L5" s="23"/>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="23"/>
-      <c r="P5" s="23"/>
-      <c r="Q5" s="23"/>
-      <c r="R5" s="23"/>
-      <c r="S5" s="23"/>
-      <c r="T5" s="23"/>
-      <c r="U5" s="23"/>
-      <c r="V5" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="W5" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="X5" s="26" t="s">
-        <v>186</v>
+      <c r="H12" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="O12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="P12" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="R12" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="S12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="T12" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="U12" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="V12" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="W12" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="X12" s="13" t="s">
+        <v>171</v>
       </c>
     </row>
-    <row r="6" spans="1:44">
-      <c r="A6" s="23">
-        <v>45914</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>111</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="G6" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="23"/>
-      <c r="K6" s="23"/>
-      <c r="L6" s="23"/>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="23"/>
-      <c r="P6" s="23"/>
-      <c r="Q6" s="23"/>
-      <c r="R6" s="23"/>
-      <c r="S6" s="23"/>
-      <c r="T6" s="23"/>
-      <c r="U6" s="23"/>
-      <c r="V6" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="W6" s="26" t="s">
-        <v>151</v>
-      </c>
-      <c r="X6" s="26" t="s">
-        <v>152</v>
+    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
+        <v>45915</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="H13" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
+      <c r="O13" s="14"/>
+      <c r="P13" s="14"/>
+      <c r="Q13" s="14"/>
+      <c r="R13" s="14"/>
+      <c r="S13" s="14"/>
+      <c r="T13" s="14"/>
+      <c r="U13" s="14"/>
+      <c r="V13" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="W13" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="X13" s="14" t="s">
+        <v>163</v>
       </c>
     </row>
-    <row r="7" spans="1:44">
-      <c r="A7" s="23">
-        <v>45911</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>195</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E7" s="26" t="s">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
+        <v>45915</v>
+      </c>
+      <c r="B14" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="F7" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>73</v>
-      </c>
-      <c r="H7" s="26" t="s">
-        <v>194</v>
-      </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="23"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-      <c r="O7" s="23"/>
-      <c r="P7" s="23"/>
-      <c r="Q7" s="23"/>
-      <c r="R7" s="23"/>
-      <c r="S7" s="23"/>
-      <c r="T7" s="23"/>
-      <c r="U7" s="23"/>
-      <c r="V7" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="W7" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="X7" s="26" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="8" spans="1:44">
-      <c r="A8" s="23">
-        <v>45892</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="23"/>
-      <c r="K8" s="23"/>
-      <c r="L8" s="23"/>
-      <c r="M8" s="23"/>
-      <c r="N8" s="23"/>
-      <c r="O8" s="23"/>
-      <c r="P8" s="23"/>
-      <c r="Q8" s="23"/>
-      <c r="R8" s="23"/>
-      <c r="S8" s="23"/>
-      <c r="T8" s="23"/>
-      <c r="U8" s="23"/>
-      <c r="V8" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="W8" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="X8" s="26" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:44">
-      <c r="A9" s="10">
-        <v>45889</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="W9" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="X9" s="21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="10" spans="1:44">
-      <c r="A10" s="10">
-        <v>45891</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="W10" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="X10" s="21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="11" spans="1:44">
-      <c r="A11" s="10">
-        <v>45904</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="W11" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="X11" s="21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="12" spans="1:44">
-      <c r="A12" s="14">
-        <v>45997</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D12" s="11" t="s">
+      <c r="C14" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="E12" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="G12" s="11" t="s">
+      <c r="F14" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="11"/>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="11"/>
-      <c r="N12" s="11"/>
-      <c r="O12" s="11"/>
-      <c r="P12" s="11"/>
-      <c r="Q12" s="11"/>
-      <c r="R12" s="11"/>
-      <c r="S12" s="11"/>
-      <c r="T12" s="11"/>
-      <c r="U12" s="11"/>
-      <c r="V12" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="W12" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="X12" s="13" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="13" spans="1:44">
-      <c r="A13" s="14">
-        <v>45926</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="H13" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M13" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N13" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="O13" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="P13" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q13" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="R13" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="S13" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="T13" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="U13" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="V13" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="W13" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="X13" s="13" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="14" spans="1:44">
-      <c r="A14" s="14">
-        <v>45941</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>21</v>
-      </c>
       <c r="H14" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="I14" s="11"/>
       <c r="J14" s="11"/>
@@ -2168,39 +2188,39 @@
       <c r="T14" s="11"/>
       <c r="U14" s="11"/>
       <c r="V14" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="W14" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="X14" s="13" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
+        <v>45914</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="W14" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="X14" s="13" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="15" spans="1:44">
-      <c r="A15" s="14">
-        <v>45982</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>132</v>
+      <c r="E15" s="11" t="s">
+        <v>86</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G15" s="11" t="s">
         <v>28</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="11"/>
@@ -2216,423 +2236,423 @@
       <c r="T15" s="11"/>
       <c r="U15" s="11"/>
       <c r="V15" s="11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="W15" s="13" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="X15" s="13" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A16" s="22">
+        <v>45914</v>
+      </c>
+      <c r="B16" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="22"/>
+      <c r="O16" s="22"/>
+      <c r="P16" s="22"/>
+      <c r="Q16" s="22"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="22"/>
+      <c r="V16" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="W16" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="X16" s="25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A17" s="21">
+        <v>45907</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W17" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="X17" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A18" s="22">
+        <v>45905</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="F18" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="22"/>
+      <c r="N18" s="22"/>
+      <c r="O18" s="22"/>
+      <c r="P18" s="22"/>
+      <c r="Q18" s="22"/>
+      <c r="R18" s="22"/>
+      <c r="S18" s="22"/>
+      <c r="T18" s="22"/>
+      <c r="U18" s="22"/>
+      <c r="V18" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="W18" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="X18" s="25" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A19" s="10">
+        <v>45904</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>208</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+      <c r="P19" s="10"/>
+      <c r="Q19" s="10"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="10"/>
+      <c r="T19" s="10"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="W19" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="X19" s="20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A20" s="7">
+        <v>45901</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H20" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="16"/>
+      <c r="Q20" s="16"/>
+      <c r="R20" s="16"/>
+      <c r="S20" s="16"/>
+      <c r="T20" s="16"/>
+      <c r="U20" s="16"/>
+      <c r="V20" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W20" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="X20" s="19" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A21" s="22">
+        <v>45900</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>180</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>179</v>
+      </c>
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="22"/>
+      <c r="N21" s="22"/>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22"/>
+      <c r="Q21" s="22"/>
+      <c r="R21" s="22"/>
+      <c r="S21" s="22"/>
+      <c r="T21" s="22"/>
+      <c r="U21" s="22"/>
+      <c r="V21" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="W21" s="25" t="s">
         <v>145</v>
       </c>
+      <c r="X21" s="25" t="s">
+        <v>177</v>
+      </c>
     </row>
-    <row r="16" spans="1:44">
-      <c r="A16" s="14">
-        <v>45915</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="11" t="s">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A22" s="26">
+        <v>45900</v>
+      </c>
+      <c r="B22" s="23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+      <c r="L22" s="23"/>
+      <c r="M22" s="23"/>
+      <c r="N22" s="23"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="23"/>
+      <c r="Q22" s="23"/>
+      <c r="R22" s="23"/>
+      <c r="S22" s="23"/>
+      <c r="T22" s="23"/>
+      <c r="U22" s="23"/>
+      <c r="V22" s="23" t="s">
         <v>69</v>
       </c>
-      <c r="E16" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="11" t="s">
+      <c r="W22" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="X22" s="24" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A23" s="21">
+        <v>45899</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="11"/>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
-      <c r="R16" s="11"/>
-      <c r="S16" s="11"/>
-      <c r="T16" s="11"/>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="W16" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="X16" s="13" t="s">
-        <v>184</v>
+      <c r="H23" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="W23" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="X23" s="15" t="s">
+        <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:24">
-      <c r="A17" s="14">
-        <v>45914</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="W17" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="X17" s="13" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24">
-      <c r="A18" s="14">
-        <v>45915</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D18" s="14" t="s">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A24" s="21">
+        <v>45898</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G24" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F18" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="G18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H18" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="14"/>
-      <c r="N18" s="14"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
-      <c r="U18" s="14"/>
-      <c r="V18" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="W18" s="14" t="s">
-        <v>173</v>
-      </c>
-      <c r="X18" s="14" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24">
-      <c r="A19" s="14">
-        <v>46059</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" s="14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D19" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="E19" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="F19" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="G19" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
-      <c r="Q19" s="14"/>
-      <c r="R19" s="14"/>
-      <c r="S19" s="14"/>
-      <c r="T19" s="14"/>
-      <c r="U19" s="14"/>
-      <c r="V19" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="W19" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="X19" s="14" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24">
-      <c r="A20" s="14">
-        <v>46011</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D20" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F20" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="I20" s="11"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="11"/>
-      <c r="N20" s="11"/>
-      <c r="O20" s="11"/>
-      <c r="P20" s="11"/>
-      <c r="Q20" s="11"/>
-      <c r="R20" s="11"/>
-      <c r="S20" s="11"/>
-      <c r="T20" s="11"/>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="W20" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="X20" s="13" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24">
-      <c r="A21" s="7">
-        <v>45889</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-      <c r="K21" s="17"/>
-      <c r="L21" s="17"/>
-      <c r="M21" s="17"/>
-      <c r="N21" s="17"/>
-      <c r="O21" s="17"/>
-      <c r="P21" s="17"/>
-      <c r="Q21" s="17"/>
-      <c r="R21" s="17"/>
-      <c r="S21" s="17"/>
-      <c r="T21" s="17"/>
-      <c r="U21" s="17"/>
-      <c r="V21" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="W21" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="X21" s="20" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24">
-      <c r="A22" s="7">
-        <v>45890</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E22" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-      <c r="K22" s="17"/>
-      <c r="L22" s="17"/>
-      <c r="M22" s="17"/>
-      <c r="N22" s="17"/>
-      <c r="O22" s="17"/>
-      <c r="P22" s="17"/>
-      <c r="Q22" s="17"/>
-      <c r="R22" s="17"/>
-      <c r="S22" s="17"/>
-      <c r="T22" s="17"/>
-      <c r="U22" s="17"/>
-      <c r="V22" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="W22" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="X22" s="20" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24">
-      <c r="A23" s="7">
-        <v>45901</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-      <c r="K23" s="17"/>
-      <c r="L23" s="17"/>
-      <c r="M23" s="17"/>
-      <c r="N23" s="17"/>
-      <c r="O23" s="17"/>
-      <c r="P23" s="17"/>
-      <c r="Q23" s="17"/>
-      <c r="R23" s="17"/>
-      <c r="S23" s="17"/>
-      <c r="T23" s="17"/>
-      <c r="U23" s="17"/>
-      <c r="V23" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="W23" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="X23" s="20" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24">
-      <c r="A24" s="22">
-        <v>45907</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>218</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>202</v>
+      <c r="H24" s="15" t="s">
+        <v>219</v>
       </c>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -2648,39 +2668,39 @@
       <c r="T24" s="6"/>
       <c r="U24" s="6"/>
       <c r="V24" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="W24" s="16" t="s">
-        <v>167</v>
-      </c>
-      <c r="X24" s="16" t="s">
-        <v>168</v>
+        <v>70</v>
+      </c>
+      <c r="W24" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="X24" s="15" t="s">
+        <v>165</v>
       </c>
     </row>
-    <row r="25" spans="1:24">
-      <c r="A25" s="22">
-        <v>45909</v>
+    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A25" s="21">
+        <v>45896</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>115</v>
+        <v>193</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>182</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E25" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F25" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F25" s="5" t="s">
-        <v>70</v>
-      </c>
       <c r="G25" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>203</v>
+        <v>28</v>
+      </c>
+      <c r="H25" s="15" t="s">
+        <v>221</v>
       </c>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
@@ -2696,39 +2716,39 @@
       <c r="T25" s="6"/>
       <c r="U25" s="6"/>
       <c r="V25" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="W25" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="X25" s="16" t="s">
-        <v>166</v>
+        <v>69</v>
+      </c>
+      <c r="W25" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="X25" s="15" t="s">
+        <v>176</v>
       </c>
     </row>
-    <row r="26" spans="1:24">
-      <c r="A26" s="22">
-        <v>45896</v>
+    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A26" s="21">
+        <v>45893</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>193</v>
+        <v>194</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>182</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>212</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G26" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="H26" s="16" t="s">
-        <v>210</v>
+      <c r="H26" s="15" t="s">
+        <v>218</v>
       </c>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
@@ -2744,268 +2764,279 @@
       <c r="T26" s="6"/>
       <c r="U26" s="6"/>
       <c r="V26" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="W26" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="X26" s="16" t="s">
-        <v>187</v>
+        <v>69</v>
+      </c>
+      <c r="W26" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="X26" s="15" t="s">
+        <v>149</v>
       </c>
     </row>
-    <row r="27" spans="1:24">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A27" s="22">
-        <v>45899</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G27" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>211</v>
-      </c>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="M27" s="6"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="6"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="6"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="W27" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="X27" s="16" t="s">
-        <v>160</v>
+        <v>45892</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="G27" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="H27" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
+      <c r="S27" s="22"/>
+      <c r="T27" s="22"/>
+      <c r="U27" s="22"/>
+      <c r="V27" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="W27" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="X27" s="25" t="s">
+        <v>140</v>
       </c>
     </row>
-    <row r="28" spans="1:24">
-      <c r="A28" s="22">
-        <v>45900</v>
-      </c>
-      <c r="B28" s="5" t="s">
+    <row r="28" spans="1:44" s="27" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="7">
+        <v>45890</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H28" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16"/>
+      <c r="P28" s="16"/>
+      <c r="Q28" s="16"/>
+      <c r="R28" s="16"/>
+      <c r="S28" s="16"/>
+      <c r="T28" s="16"/>
+      <c r="U28" s="16"/>
+      <c r="V28" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W28" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="X28" s="19" t="s">
+        <v>206</v>
+      </c>
+      <c r="Y28"/>
+      <c r="Z28"/>
+      <c r="AA28"/>
+      <c r="AB28"/>
+      <c r="AC28"/>
+      <c r="AD28"/>
+      <c r="AE28"/>
+      <c r="AF28"/>
+      <c r="AG28"/>
+      <c r="AH28"/>
+      <c r="AI28"/>
+      <c r="AJ28"/>
+      <c r="AK28"/>
+      <c r="AL28"/>
+      <c r="AM28"/>
+      <c r="AN28"/>
+      <c r="AO28"/>
+      <c r="AP28"/>
+      <c r="AQ28"/>
+      <c r="AR28"/>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A29" s="7">
+        <v>45889</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H29" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="16"/>
+      <c r="N29" s="16"/>
+      <c r="O29" s="16"/>
+      <c r="P29" s="16"/>
+      <c r="Q29" s="16"/>
+      <c r="R29" s="16"/>
+      <c r="S29" s="16"/>
+      <c r="T29" s="16"/>
+      <c r="U29" s="16"/>
+      <c r="V29" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="W29" s="19" t="s">
+        <v>202</v>
+      </c>
+      <c r="X29" s="19" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="30" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A30" s="22">
+        <v>45889</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G28" s="6" t="s">
+      <c r="D30" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="E30" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="F30" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="H28" s="16" t="s">
-        <v>212</v>
-      </c>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6"/>
-      <c r="O28" s="6"/>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="T28" s="6"/>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="W28" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="X28" s="16" t="s">
-        <v>159</v>
+      <c r="H30" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="22"/>
+      <c r="N30" s="22"/>
+      <c r="O30" s="22"/>
+      <c r="P30" s="22"/>
+      <c r="Q30" s="22"/>
+      <c r="R30" s="22"/>
+      <c r="S30" s="22"/>
+      <c r="T30" s="22"/>
+      <c r="U30" s="22"/>
+      <c r="V30" s="22" t="s">
+        <v>69</v>
+      </c>
+      <c r="W30" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="X30" s="25" t="s">
+        <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:24">
-      <c r="A29" s="22">
-        <v>45898</v>
-      </c>
-      <c r="B29" s="5" t="s">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A31" s="10">
+        <v>45889</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10"/>
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+      <c r="P31" s="10"/>
+      <c r="Q31" s="10"/>
+      <c r="R31" s="10"/>
+      <c r="S31" s="10"/>
+      <c r="T31" s="10"/>
+      <c r="U31" s="10"/>
+      <c r="V31" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="W31" s="20" t="s">
         <v>200</v>
       </c>
-      <c r="C29" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
-      <c r="K29" s="6"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="6"/>
-      <c r="N29" s="6"/>
-      <c r="O29" s="6"/>
-      <c r="P29" s="6"/>
-      <c r="Q29" s="6"/>
-      <c r="R29" s="6"/>
-      <c r="S29" s="6"/>
-      <c r="T29" s="6"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="W29" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="X29" s="16" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24">
-      <c r="A30" s="22">
-        <v>45893</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>193</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="G30" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>214</v>
-      </c>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
-      <c r="M30" s="6"/>
-      <c r="N30" s="6"/>
-      <c r="O30" s="6"/>
-      <c r="P30" s="6"/>
-      <c r="Q30" s="6"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="W30" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="X30" s="16" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24">
-      <c r="A31" s="22">
-        <v>46059</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H31" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6"/>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="6"/>
-      <c r="S31" s="6"/>
-      <c r="T31" s="6"/>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="W31" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="X31" s="16" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24">
-      <c r="B32" s="15"/>
-      <c r="G32" s="15"/>
-    </row>
-    <row r="33" spans="2:2">
-      <c r="B33" s="15" t="s">
-        <v>92</v>
+      <c r="X31" s="20" t="s">
+        <v>197</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:FI31" xr:uid="{00000000-0009-0000-0000-000000000000}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AR31">
-      <sortCondition ref="H1:H31"/>
+      <sortCondition descending="1" ref="A1:A31"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="4" type="noConversion"/>
@@ -3017,7 +3048,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
